--- a/healthcare_assessment_forms/022_learning_and_memory_assessment--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/022_learning_and_memory_assessment--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'drive'}</t>
+          <t>drive</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Drive'}</t>
+          <t>Drive</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'public_transportation'}</t>
+          <t>public_transportation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Public transportation'}</t>
+          <t>Public transportation</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
